--- a/business_forms/016_cards_for_a_cause_order_form--business_forms.xlsx
+++ b/business_forms/016_cards_for_a_cause_order_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -877,8 +877,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -906,12 +906,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'all_occasion_box_1',_'value':_'all_occasion_1'}</t>
+          <t>all_occasion_box_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'All Occasion Box 1', 'value': 'all_occasion_1'}</t>
+          <t>All Occasion Box 1</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'all_occasion_box_2',_'value':_'all_occasion_2'}</t>
+          <t>all_occasion_box_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'All Occasion Box 2', 'value': 'all_occasion_2'}</t>
+          <t>All Occasion Box 2</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'kids_birthday_box',_'value':_'kids_birthday'}</t>
+          <t>kids_birthday_box</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Kids Birthday Box', 'value': 'kids_birthday'}</t>
+          <t>Kids Birthday Box</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'thanks_&amp;_blanks_box',_'value':_'thanks_blanks'}</t>
+          <t>thanks_&amp;_blanks_box</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Thanks &amp; Blanks Box', 'value': 'thanks_blanks'}</t>
+          <t>Thanks &amp; Blanks Box</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'holiday_card_box',_'value':_'holiday'}</t>
+          <t>holiday_card_box</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Holiday Card Box', 'value': 'holiday'}</t>
+          <t>Holiday Card Box</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'pickup_from_organization',_'value':_'pickup'}</t>
+          <t>pickup_from_organization</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Pickup from Organization', 'value': 'pickup'}</t>
+          <t>Pickup from Organization</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'ship_to_my_address_(extra_fee)',_'value':_'shipping'}</t>
+          <t>ship_to_my_address_(extra_fee)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Ship to My Address (Extra Fee)', 'value': 'shipping'}</t>
+          <t>Ship to My Address (Extra Fee)</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'local_delivery_(available_for_some_areas)',_'value':_'local_delivery'}</t>
+          <t>local_delivery_(available_for_some_areas)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Local Delivery (Available for some areas)', 'value': 'local_delivery'}</t>
+          <t>Local Delivery (Available for some areas)</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'credit/debit_card_(online)',_'value':_'card'}</t>
+          <t>credit/debit_card_(online)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Credit/Debit Card (Online)', 'value': 'card'}</t>
+          <t>Credit/Debit Card (Online)</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'cash_(at_pickup_only)',_'value':_'cash'}</t>
+          <t>cash_(at_pickup_only)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Cash (at pickup only)', 'value': 'cash'}</t>
+          <t>Cash (at pickup only)</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'check_(payable_to_organization)',_'value':_'check'}</t>
+          <t>check_(payable_to_organization)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Check (payable to organization)', 'value': 'check'}</t>
+          <t>Check (payable to organization)</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'i_confirm',_'value':_'confirmed'}</t>
+          <t>i_confirm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'I Confirm', 'value': 'confirmed'}</t>
+          <t>I Confirm</t>
         </is>
       </c>
     </row>
